--- a/avito-feed-construction/fleet-construction.xlsx
+++ b/avito-feed-construction/fleet-construction.xlsx
@@ -842,7 +842,11 @@
         </is>
       </c>
       <c r="Z2" s="1" t="inlineStr"/>
-      <c r="AA2" s="1" t="inlineStr"/>
+      <c r="AA2" s="1" t="inlineStr">
+        <is>
+          <t>10800000</t>
+        </is>
+      </c>
       <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
@@ -1002,7 +1006,11 @@
         </is>
       </c>
       <c r="Z3" s="1" t="inlineStr"/>
-      <c r="AA3" s="1" t="inlineStr"/>
+      <c r="AA3" s="1" t="inlineStr">
+        <is>
+          <t>10800000</t>
+        </is>
+      </c>
       <c r="AB3" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
@@ -1162,7 +1170,11 @@
         </is>
       </c>
       <c r="Z4" s="1" t="inlineStr"/>
-      <c r="AA4" s="1" t="inlineStr"/>
+      <c r="AA4" s="1" t="inlineStr">
+        <is>
+          <t>10800000</t>
+        </is>
+      </c>
       <c r="AB4" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
@@ -1322,7 +1334,11 @@
         </is>
       </c>
       <c r="Z5" s="1" t="inlineStr"/>
-      <c r="AA5" s="1" t="inlineStr"/>
+      <c r="AA5" s="1" t="inlineStr">
+        <is>
+          <t>10800000</t>
+        </is>
+      </c>
       <c r="AB5" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
@@ -1482,7 +1498,11 @@
         </is>
       </c>
       <c r="Z6" s="1" t="inlineStr"/>
-      <c r="AA6" s="1" t="inlineStr"/>
+      <c r="AA6" s="1" t="inlineStr">
+        <is>
+          <t>10000000</t>
+        </is>
+      </c>
       <c r="AB6" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
@@ -1642,7 +1662,11 @@
         </is>
       </c>
       <c r="Z7" s="1" t="inlineStr"/>
-      <c r="AA7" s="1" t="inlineStr"/>
+      <c r="AA7" s="1" t="inlineStr">
+        <is>
+          <t>14500000</t>
+        </is>
+      </c>
       <c r="AB7" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
@@ -1802,7 +1826,11 @@
         </is>
       </c>
       <c r="Z8" s="1" t="inlineStr"/>
-      <c r="AA8" s="1" t="inlineStr"/>
+      <c r="AA8" s="1" t="inlineStr">
+        <is>
+          <t>14500000</t>
+        </is>
+      </c>
       <c r="AB8" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
@@ -1962,7 +1990,11 @@
         </is>
       </c>
       <c r="Z9" s="1" t="inlineStr"/>
-      <c r="AA9" s="1" t="inlineStr"/>
+      <c r="AA9" s="1" t="inlineStr">
+        <is>
+          <t>14500000</t>
+        </is>
+      </c>
       <c r="AB9" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
@@ -2122,7 +2154,11 @@
         </is>
       </c>
       <c r="Z10" s="1" t="inlineStr"/>
-      <c r="AA10" s="1" t="inlineStr"/>
+      <c r="AA10" s="1" t="inlineStr">
+        <is>
+          <t>14500000</t>
+        </is>
+      </c>
       <c r="AB10" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
@@ -2642,7 +2678,11 @@
         </is>
       </c>
       <c r="Z2" s="1" t="inlineStr"/>
-      <c r="AA2" s="1" t="inlineStr"/>
+      <c r="AA2" s="1" t="inlineStr">
+        <is>
+          <t>8800000</t>
+        </is>
+      </c>
       <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
@@ -2797,7 +2837,11 @@
         </is>
       </c>
       <c r="Z3" s="1" t="inlineStr"/>
-      <c r="AA3" s="1" t="inlineStr"/>
+      <c r="AA3" s="1" t="inlineStr">
+        <is>
+          <t>8800000</t>
+        </is>
+      </c>
       <c r="AB3" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
@@ -2952,7 +2996,11 @@
         </is>
       </c>
       <c r="Z4" s="1" t="inlineStr"/>
-      <c r="AA4" s="1" t="inlineStr"/>
+      <c r="AA4" s="1" t="inlineStr">
+        <is>
+          <t>11800000</t>
+        </is>
+      </c>
       <c r="AB4" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>
@@ -3443,7 +3491,11 @@
         </is>
       </c>
       <c r="Z2" s="1" t="inlineStr"/>
-      <c r="AA2" s="1" t="inlineStr"/>
+      <c r="AA2" s="1" t="inlineStr">
+        <is>
+          <t>19900000</t>
+        </is>
+      </c>
       <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>В наличии</t>

--- a/avito-feed-construction/fleet-construction.xlsx
+++ b/avito-feed-construction/fleet-construction.xlsx
@@ -815,7 +815,7 @@
       <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy625e/15891846-6c7e-418f-83d7-7fe2ca2cf4bb.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy625e/5b8aed55-56e0-4cc2-aa27-32c4f33bddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy625e/f0fda440-4f99-4c22-b8e7-39c341d24c3d.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy625e/571d5749-f26e-41ee-9768-0cd7a2bdcff0.JPG</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/15891846-6c7e-418f-83d7-7fe2ca2cf4bb.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/5b8aed55-56e0-4cc2-aa27-32c4f33bddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/f0fda440-4f99-4c22-b8e7-39c341d24c3d.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/571d5749-f26e-41ee-9768-0cd7a2bdcff0.JPG</t>
         </is>
       </c>
       <c r="S2" s="1" t="inlineStr"/>
@@ -979,7 +979,7 @@
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy625e/15891846-6c7e-418f-83d7-7fe2ca2cf4bb.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy625e/5b8aed55-56e0-4cc2-aa27-32c4f33bddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy625e/f0fda440-4f99-4c22-b8e7-39c341d24c3d.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy625e/571d5749-f26e-41ee-9768-0cd7a2bdcff0.JPG</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/15891846-6c7e-418f-83d7-7fe2ca2cf4bb.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/5b8aed55-56e0-4cc2-aa27-32c4f33bddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/f0fda440-4f99-4c22-b8e7-39c341d24c3d.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/571d5749-f26e-41ee-9768-0cd7a2bdcff0.JPG</t>
         </is>
       </c>
       <c r="S3" s="1" t="inlineStr"/>
@@ -1143,7 +1143,7 @@
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy625e/15891846-6c7e-418f-83d7-7fe2ca2cf4bb.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy625e/5b8aed55-56e0-4cc2-aa27-32c4f33bddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy625e/f0fda440-4f99-4c22-b8e7-39c341d24c3d.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy625e/571d5749-f26e-41ee-9768-0cd7a2bdcff0.JPG</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/15891846-6c7e-418f-83d7-7fe2ca2cf4bb.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/5b8aed55-56e0-4cc2-aa27-32c4f33bddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/f0fda440-4f99-4c22-b8e7-39c341d24c3d.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/571d5749-f26e-41ee-9768-0cd7a2bdcff0.JPG</t>
         </is>
       </c>
       <c r="S4" s="1" t="inlineStr"/>
@@ -1307,7 +1307,7 @@
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy625e/15891846-6c7e-418f-83d7-7fe2ca2cf4bb.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy625e/5b8aed55-56e0-4cc2-aa27-32c4f33bddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy625e/f0fda440-4f99-4c22-b8e7-39c341d24c3d.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy625e/571d5749-f26e-41ee-9768-0cd7a2bdcff0.JPG</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/15891846-6c7e-418f-83d7-7fe2ca2cf4bb.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/5b8aed55-56e0-4cc2-aa27-32c4f33bddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/f0fda440-4f99-4c22-b8e7-39c341d24c3d.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/571d5749-f26e-41ee-9768-0cd7a2bdcff0.JPG</t>
         </is>
       </c>
       <c r="S5" s="1" t="inlineStr"/>
@@ -1471,7 +1471,7 @@
       <c r="Q6" s="1" t="inlineStr"/>
       <c r="R6" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy625e/15891846-6c7e-418f-83d7-7fe2ca2cf4bb.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy625e/5b8aed55-56e0-4cc2-aa27-32c4f33bddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy625e/f0fda440-4f99-4c22-b8e7-39c341d24c3d.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy625e/571d5749-f26e-41ee-9768-0cd7a2bdcff0.JPG</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/15891846-6c7e-418f-83d7-7fe2ca2cf4bb.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/5b8aed55-56e0-4cc2-aa27-32c4f33bddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/f0fda440-4f99-4c22-b8e7-39c341d24c3d.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/571d5749-f26e-41ee-9768-0cd7a2bdcff0.JPG</t>
         </is>
       </c>
       <c r="S6" s="1" t="inlineStr"/>
@@ -1635,7 +1635,7 @@
       <c r="Q7" s="1" t="inlineStr"/>
       <c r="R7" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/4914ccf9-931d-4d22-9dac-be923fc1ddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/eaaf0a0e-4b85-452e-b59c-f199cc8d0fe9.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/da0b4cb8-3556-4465-87e2-9c2ca93b79d2.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/89c5e118-02a9-4f8b-a9d9-448970a1c2c3.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/f5bc4d80-9e99-4e1e-b4f3-1fe18453c34c.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/26575e22-ad8a-4e04-b2d4-0e24d12569af.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/61050b30-ffbc-4861-a747-254a02538bba.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/d5857bb6-b8f0-4fa4-ae50-1a110838b54f.JPG</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/4914ccf9-931d-4d22-9dac-be923fc1ddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/eaaf0a0e-4b85-452e-b59c-f199cc8d0fe9.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/da0b4cb8-3556-4465-87e2-9c2ca93b79d2.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/89c5e118-02a9-4f8b-a9d9-448970a1c2c3.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/f5bc4d80-9e99-4e1e-b4f3-1fe18453c34c.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/26575e22-ad8a-4e04-b2d4-0e24d12569af.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/61050b30-ffbc-4861-a747-254a02538bba.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/d5857bb6-b8f0-4fa4-ae50-1a110838b54f.JPG</t>
         </is>
       </c>
       <c r="S7" s="1" t="inlineStr"/>
@@ -1799,7 +1799,7 @@
       <c r="Q8" s="1" t="inlineStr"/>
       <c r="R8" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/4914ccf9-931d-4d22-9dac-be923fc1ddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/eaaf0a0e-4b85-452e-b59c-f199cc8d0fe9.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/da0b4cb8-3556-4465-87e2-9c2ca93b79d2.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/89c5e118-02a9-4f8b-a9d9-448970a1c2c3.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/f5bc4d80-9e99-4e1e-b4f3-1fe18453c34c.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/26575e22-ad8a-4e04-b2d4-0e24d12569af.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/61050b30-ffbc-4861-a747-254a02538bba.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/d5857bb6-b8f0-4fa4-ae50-1a110838b54f.JPG</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/4914ccf9-931d-4d22-9dac-be923fc1ddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/eaaf0a0e-4b85-452e-b59c-f199cc8d0fe9.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/da0b4cb8-3556-4465-87e2-9c2ca93b79d2.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/89c5e118-02a9-4f8b-a9d9-448970a1c2c3.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/f5bc4d80-9e99-4e1e-b4f3-1fe18453c34c.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/26575e22-ad8a-4e04-b2d4-0e24d12569af.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/61050b30-ffbc-4861-a747-254a02538bba.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/d5857bb6-b8f0-4fa4-ae50-1a110838b54f.JPG</t>
         </is>
       </c>
       <c r="S8" s="1" t="inlineStr"/>
@@ -1963,7 +1963,7 @@
       <c r="Q9" s="1" t="inlineStr"/>
       <c r="R9" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/4914ccf9-931d-4d22-9dac-be923fc1ddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/eaaf0a0e-4b85-452e-b59c-f199cc8d0fe9.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/da0b4cb8-3556-4465-87e2-9c2ca93b79d2.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/89c5e118-02a9-4f8b-a9d9-448970a1c2c3.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/f5bc4d80-9e99-4e1e-b4f3-1fe18453c34c.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/26575e22-ad8a-4e04-b2d4-0e24d12569af.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/61050b30-ffbc-4861-a747-254a02538bba.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/d5857bb6-b8f0-4fa4-ae50-1a110838b54f.JPG</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/4914ccf9-931d-4d22-9dac-be923fc1ddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/eaaf0a0e-4b85-452e-b59c-f199cc8d0fe9.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/da0b4cb8-3556-4465-87e2-9c2ca93b79d2.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/89c5e118-02a9-4f8b-a9d9-448970a1c2c3.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/f5bc4d80-9e99-4e1e-b4f3-1fe18453c34c.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/26575e22-ad8a-4e04-b2d4-0e24d12569af.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/61050b30-ffbc-4861-a747-254a02538bba.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/d5857bb6-b8f0-4fa4-ae50-1a110838b54f.JPG</t>
         </is>
       </c>
       <c r="S9" s="1" t="inlineStr"/>
@@ -2127,7 +2127,7 @@
       <c r="Q10" s="1" t="inlineStr"/>
       <c r="R10" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/4914ccf9-931d-4d22-9dac-be923fc1ddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/eaaf0a0e-4b85-452e-b59c-f199cc8d0fe9.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/da0b4cb8-3556-4465-87e2-9c2ca93b79d2.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/89c5e118-02a9-4f8b-a9d9-448970a1c2c3.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/f5bc4d80-9e99-4e1e-b4f3-1fe18453c34c.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/26575e22-ad8a-4e04-b2d4-0e24d12569af.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/61050b30-ffbc-4861-a747-254a02538bba.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy636e/d5857bb6-b8f0-4fa4-ae50-1a110838b54f.JPG</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/4914ccf9-931d-4d22-9dac-be923fc1ddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/eaaf0a0e-4b85-452e-b59c-f199cc8d0fe9.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/da0b4cb8-3556-4465-87e2-9c2ca93b79d2.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/89c5e118-02a9-4f8b-a9d9-448970a1c2c3.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/f5bc4d80-9e99-4e1e-b4f3-1fe18453c34c.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/26575e22-ad8a-4e04-b2d4-0e24d12569af.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/61050b30-ffbc-4861-a747-254a02538bba.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/d5857bb6-b8f0-4fa4-ae50-1a110838b54f.JPG</t>
         </is>
       </c>
       <c r="S10" s="1" t="inlineStr"/>
@@ -2651,7 +2651,7 @@
       <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jyl615fe/0d316b82-9b0e-4637-bafa-900ae468a21d.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jyl615fe/208fce80-93d8-4b35-b5f6-9d5ded06641e.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jyl615fe/4ab5a6ca-48a0-4bdf-82e9-b37e2b4fc552.JPG</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jyl615fe/0d316b82-9b0e-4637-bafa-900ae468a21d.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jyl615fe/208fce80-93d8-4b35-b5f6-9d5ded06641e.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jyl615fe/4ab5a6ca-48a0-4bdf-82e9-b37e2b4fc552.JPG</t>
         </is>
       </c>
       <c r="S2" s="1" t="inlineStr"/>
@@ -2810,7 +2810,7 @@
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jyl615fe/0d316b82-9b0e-4637-bafa-900ae468a21d.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jyl615fe/208fce80-93d8-4b35-b5f6-9d5ded06641e.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jyl615fe/4ab5a6ca-48a0-4bdf-82e9-b37e2b4fc552.JPG</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jyl615fe/0d316b82-9b0e-4637-bafa-900ae468a21d.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jyl615fe/208fce80-93d8-4b35-b5f6-9d5ded06641e.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jyl615fe/4ab5a6ca-48a0-4bdf-82e9-b37e2b4fc552.JPG</t>
         </is>
       </c>
       <c r="S3" s="1" t="inlineStr"/>
@@ -2969,7 +2969,7 @@
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jyl621e/cff79444-c088-4e67-9215-e825d2b7c435.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jyl621e/376c62de-5217-4f96-9d27-8bd3fa1f4723.JPG</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jyl621e/cff79444-c088-4e67-9215-e825d2b7c435.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jyl621e/376c62de-5217-4f96-9d27-8bd3fa1f4723.JPG</t>
         </is>
       </c>
       <c r="S4" s="1" t="inlineStr"/>
@@ -3464,7 +3464,7 @@
       <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy220c/43353c14-92c6-438c-a3d0-b4e19e3b9049.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy220c/ba477ea8-5aaf-496c-be56-55b5e465cf2b.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/jonyang-jy220c/8c27eb73-6266-41aa-9c02-f632a6236088.JPG</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy220c/43353c14-92c6-438c-a3d0-b4e19e3b9049.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy220c/ba477ea8-5aaf-496c-be56-55b5e465cf2b.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy220c/8c27eb73-6266-41aa-9c02-f632a6236088.JPG</t>
         </is>
       </c>
       <c r="S2" s="1" t="inlineStr"/>

--- a/avito-feed-construction/fleet-construction.xlsx
+++ b/avito-feed-construction/fleet-construction.xlsx
@@ -815,7 +815,7 @@
       <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/15891846-6c7e-418f-83d7-7fe2ca2cf4bb.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/5b8aed55-56e0-4cc2-aa27-32c4f33bddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/f0fda440-4f99-4c22-b8e7-39c341d24c3d.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/571d5749-f26e-41ee-9768-0cd7a2bdcff0.JPG</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/15891846-6c7e-418f-83d7-7fe2ca2cf4bb.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/5b8aed55-56e0-4cc2-aa27-32c4f33bddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/f0fda440-4f99-4c22-b8e7-39c341d24c3d.JPG</t>
         </is>
       </c>
       <c r="S2" s="1" t="inlineStr"/>
@@ -979,7 +979,7 @@
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/15891846-6c7e-418f-83d7-7fe2ca2cf4bb.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/5b8aed55-56e0-4cc2-aa27-32c4f33bddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/f0fda440-4f99-4c22-b8e7-39c341d24c3d.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/571d5749-f26e-41ee-9768-0cd7a2bdcff0.JPG</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/15891846-6c7e-418f-83d7-7fe2ca2cf4bb.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/5b8aed55-56e0-4cc2-aa27-32c4f33bddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/f0fda440-4f99-4c22-b8e7-39c341d24c3d.JPG</t>
         </is>
       </c>
       <c r="S3" s="1" t="inlineStr"/>
@@ -1143,7 +1143,7 @@
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/15891846-6c7e-418f-83d7-7fe2ca2cf4bb.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/5b8aed55-56e0-4cc2-aa27-32c4f33bddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/f0fda440-4f99-4c22-b8e7-39c341d24c3d.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/571d5749-f26e-41ee-9768-0cd7a2bdcff0.JPG</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/15891846-6c7e-418f-83d7-7fe2ca2cf4bb.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/5b8aed55-56e0-4cc2-aa27-32c4f33bddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/f0fda440-4f99-4c22-b8e7-39c341d24c3d.JPG</t>
         </is>
       </c>
       <c r="S4" s="1" t="inlineStr"/>
@@ -1307,7 +1307,7 @@
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/15891846-6c7e-418f-83d7-7fe2ca2cf4bb.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/5b8aed55-56e0-4cc2-aa27-32c4f33bddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/f0fda440-4f99-4c22-b8e7-39c341d24c3d.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/571d5749-f26e-41ee-9768-0cd7a2bdcff0.JPG</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/15891846-6c7e-418f-83d7-7fe2ca2cf4bb.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/5b8aed55-56e0-4cc2-aa27-32c4f33bddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/f0fda440-4f99-4c22-b8e7-39c341d24c3d.JPG</t>
         </is>
       </c>
       <c r="S5" s="1" t="inlineStr"/>
@@ -1471,7 +1471,7 @@
       <c r="Q6" s="1" t="inlineStr"/>
       <c r="R6" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/15891846-6c7e-418f-83d7-7fe2ca2cf4bb.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/5b8aed55-56e0-4cc2-aa27-32c4f33bddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/f0fda440-4f99-4c22-b8e7-39c341d24c3d.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/571d5749-f26e-41ee-9768-0cd7a2bdcff0.JPG</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/15891846-6c7e-418f-83d7-7fe2ca2cf4bb.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/5b8aed55-56e0-4cc2-aa27-32c4f33bddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy625e/f0fda440-4f99-4c22-b8e7-39c341d24c3d.JPG</t>
         </is>
       </c>
       <c r="S6" s="1" t="inlineStr"/>
@@ -1635,7 +1635,7 @@
       <c r="Q7" s="1" t="inlineStr"/>
       <c r="R7" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/4914ccf9-931d-4d22-9dac-be923fc1ddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/eaaf0a0e-4b85-452e-b59c-f199cc8d0fe9.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/da0b4cb8-3556-4465-87e2-9c2ca93b79d2.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/89c5e118-02a9-4f8b-a9d9-448970a1c2c3.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/f5bc4d80-9e99-4e1e-b4f3-1fe18453c34c.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/26575e22-ad8a-4e04-b2d4-0e24d12569af.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/61050b30-ffbc-4861-a747-254a02538bba.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/d5857bb6-b8f0-4fa4-ae50-1a110838b54f.JPG</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/4914ccf9-931d-4d22-9dac-be923fc1ddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/eaaf0a0e-4b85-452e-b59c-f199cc8d0fe9.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/da0b4cb8-3556-4465-87e2-9c2ca93b79d2.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/89c5e118-02a9-4f8b-a9d9-448970a1c2c3.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/f5bc4d80-9e99-4e1e-b4f3-1fe18453c34c.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/26575e22-ad8a-4e04-b2d4-0e24d12569af.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/61050b30-ffbc-4861-a747-254a02538bba.JPG</t>
         </is>
       </c>
       <c r="S7" s="1" t="inlineStr"/>
@@ -1799,7 +1799,7 @@
       <c r="Q8" s="1" t="inlineStr"/>
       <c r="R8" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/4914ccf9-931d-4d22-9dac-be923fc1ddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/eaaf0a0e-4b85-452e-b59c-f199cc8d0fe9.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/da0b4cb8-3556-4465-87e2-9c2ca93b79d2.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/89c5e118-02a9-4f8b-a9d9-448970a1c2c3.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/f5bc4d80-9e99-4e1e-b4f3-1fe18453c34c.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/26575e22-ad8a-4e04-b2d4-0e24d12569af.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/61050b30-ffbc-4861-a747-254a02538bba.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/d5857bb6-b8f0-4fa4-ae50-1a110838b54f.JPG</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/4914ccf9-931d-4d22-9dac-be923fc1ddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/eaaf0a0e-4b85-452e-b59c-f199cc8d0fe9.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/da0b4cb8-3556-4465-87e2-9c2ca93b79d2.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/89c5e118-02a9-4f8b-a9d9-448970a1c2c3.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/f5bc4d80-9e99-4e1e-b4f3-1fe18453c34c.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/26575e22-ad8a-4e04-b2d4-0e24d12569af.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/61050b30-ffbc-4861-a747-254a02538bba.JPG</t>
         </is>
       </c>
       <c r="S8" s="1" t="inlineStr"/>
@@ -1963,7 +1963,7 @@
       <c r="Q9" s="1" t="inlineStr"/>
       <c r="R9" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/4914ccf9-931d-4d22-9dac-be923fc1ddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/eaaf0a0e-4b85-452e-b59c-f199cc8d0fe9.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/da0b4cb8-3556-4465-87e2-9c2ca93b79d2.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/89c5e118-02a9-4f8b-a9d9-448970a1c2c3.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/f5bc4d80-9e99-4e1e-b4f3-1fe18453c34c.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/26575e22-ad8a-4e04-b2d4-0e24d12569af.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/61050b30-ffbc-4861-a747-254a02538bba.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/d5857bb6-b8f0-4fa4-ae50-1a110838b54f.JPG</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/4914ccf9-931d-4d22-9dac-be923fc1ddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/eaaf0a0e-4b85-452e-b59c-f199cc8d0fe9.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/da0b4cb8-3556-4465-87e2-9c2ca93b79d2.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/89c5e118-02a9-4f8b-a9d9-448970a1c2c3.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/f5bc4d80-9e99-4e1e-b4f3-1fe18453c34c.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/26575e22-ad8a-4e04-b2d4-0e24d12569af.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/61050b30-ffbc-4861-a747-254a02538bba.JPG</t>
         </is>
       </c>
       <c r="S9" s="1" t="inlineStr"/>
@@ -2127,7 +2127,7 @@
       <c r="Q10" s="1" t="inlineStr"/>
       <c r="R10" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/4914ccf9-931d-4d22-9dac-be923fc1ddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/eaaf0a0e-4b85-452e-b59c-f199cc8d0fe9.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/da0b4cb8-3556-4465-87e2-9c2ca93b79d2.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/89c5e118-02a9-4f8b-a9d9-448970a1c2c3.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/f5bc4d80-9e99-4e1e-b4f3-1fe18453c34c.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/26575e22-ad8a-4e04-b2d4-0e24d12569af.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/61050b30-ffbc-4861-a747-254a02538bba.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/d5857bb6-b8f0-4fa4-ae50-1a110838b54f.JPG</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/4914ccf9-931d-4d22-9dac-be923fc1ddc8.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/eaaf0a0e-4b85-452e-b59c-f199cc8d0fe9.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/da0b4cb8-3556-4465-87e2-9c2ca93b79d2.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/89c5e118-02a9-4f8b-a9d9-448970a1c2c3.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/f5bc4d80-9e99-4e1e-b4f3-1fe18453c34c.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/26575e22-ad8a-4e04-b2d4-0e24d12569af.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jy636e/61050b30-ffbc-4861-a747-254a02538bba.JPG</t>
         </is>
       </c>
       <c r="S10" s="1" t="inlineStr"/>
@@ -2651,7 +2651,7 @@
       <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jyl615fe/0d316b82-9b0e-4637-bafa-900ae468a21d.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jyl615fe/208fce80-93d8-4b35-b5f6-9d5ded06641e.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jyl615fe/4ab5a6ca-48a0-4bdf-82e9-b37e2b4fc552.JPG</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jyl615fe/0d316b82-9b0e-4637-bafa-900ae468a21d.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jyl615fe/208fce80-93d8-4b35-b5f6-9d5ded06641e.JPG</t>
         </is>
       </c>
       <c r="S2" s="1" t="inlineStr"/>
@@ -2810,7 +2810,7 @@
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jyl615fe/0d316b82-9b0e-4637-bafa-900ae468a21d.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jyl615fe/208fce80-93d8-4b35-b5f6-9d5ded06641e.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jyl615fe/4ab5a6ca-48a0-4bdf-82e9-b37e2b4fc552.JPG</t>
+          <t>https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jyl615fe/0d316b82-9b0e-4637-bafa-900ae468a21d.JPG | https://raw.githubusercontent.com/aj123123-hub/belkar-avito-feed/main/avito-feed-construction/photos/jonyang-jyl615fe/208fce80-93d8-4b35-b5f6-9d5ded06641e.JPG</t>
         </is>
       </c>
       <c r="S3" s="1" t="inlineStr"/>

--- a/avito-feed-construction/fleet-construction.xlsx
+++ b/avito-feed-construction/fleet-construction.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="AB2" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>Под заказ</t>
         </is>
       </c>
       <c r="AC2" s="1" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AB3" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>Под заказ</t>
         </is>
       </c>
       <c r="AC3" s="1" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="AB4" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>Под заказ</t>
         </is>
       </c>
       <c r="AC4" s="1" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="AB5" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>Под заказ</t>
         </is>
       </c>
       <c r="AC5" s="1" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="AB6" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>Под заказ</t>
         </is>
       </c>
       <c r="AC6" s="1" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AB7" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>Под заказ</t>
         </is>
       </c>
       <c r="AC7" s="1" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AB8" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>Под заказ</t>
         </is>
       </c>
       <c r="AC8" s="1" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="AB9" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>Под заказ</t>
         </is>
       </c>
       <c r="AC9" s="1" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="AB10" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>Под заказ</t>
         </is>
       </c>
       <c r="AC10" s="1" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="AB2" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>Под заказ</t>
         </is>
       </c>
       <c r="AC2" s="1" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="AB3" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>Под заказ</t>
         </is>
       </c>
       <c r="AC3" s="1" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="AB4" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>Под заказ</t>
         </is>
       </c>
       <c r="AC4" s="1" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="AB2" s="1" t="inlineStr">
         <is>
-          <t>В наличии</t>
+          <t>Под заказ</t>
         </is>
       </c>
       <c r="AC2" s="1" t="inlineStr">

--- a/avito-feed-construction/fleet-construction.xlsx
+++ b/avito-feed-construction/fleet-construction.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Гусеничные экскаваторы" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Колёсные экскаваторы" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Бульдозеры" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Гусеничные экскаваторы" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Колёсные экскаваторы" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Бульдозеры" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -783,7 +783,11 @@
       <c r="E2" s="1" t="inlineStr"/>
       <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" s="1" t="inlineStr"/>
-      <c r="H2" s="1" t="inlineStr"/>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
@@ -947,7 +951,11 @@
       <c r="E3" s="1" t="inlineStr"/>
       <c r="F3" s="1" t="inlineStr"/>
       <c r="G3" s="1" t="inlineStr"/>
-      <c r="H3" s="1" t="inlineStr"/>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
@@ -1111,7 +1119,11 @@
       <c r="E4" s="1" t="inlineStr"/>
       <c r="F4" s="1" t="inlineStr"/>
       <c r="G4" s="1" t="inlineStr"/>
-      <c r="H4" s="1" t="inlineStr"/>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
@@ -1275,7 +1287,11 @@
       <c r="E5" s="1" t="inlineStr"/>
       <c r="F5" s="1" t="inlineStr"/>
       <c r="G5" s="1" t="inlineStr"/>
-      <c r="H5" s="1" t="inlineStr"/>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
@@ -1439,7 +1455,11 @@
       <c r="E6" s="1" t="inlineStr"/>
       <c r="F6" s="1" t="inlineStr"/>
       <c r="G6" s="1" t="inlineStr"/>
-      <c r="H6" s="1" t="inlineStr"/>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
@@ -1603,7 +1623,11 @@
       <c r="E7" s="1" t="inlineStr"/>
       <c r="F7" s="1" t="inlineStr"/>
       <c r="G7" s="1" t="inlineStr"/>
-      <c r="H7" s="1" t="inlineStr"/>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
@@ -1767,7 +1791,11 @@
       <c r="E8" s="1" t="inlineStr"/>
       <c r="F8" s="1" t="inlineStr"/>
       <c r="G8" s="1" t="inlineStr"/>
-      <c r="H8" s="1" t="inlineStr"/>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
@@ -1931,7 +1959,11 @@
       <c r="E9" s="1" t="inlineStr"/>
       <c r="F9" s="1" t="inlineStr"/>
       <c r="G9" s="1" t="inlineStr"/>
-      <c r="H9" s="1" t="inlineStr"/>
+      <c r="H9" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
@@ -2095,7 +2127,11 @@
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr"/>
       <c r="G10" s="1" t="inlineStr"/>
-      <c r="H10" s="1" t="inlineStr"/>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
@@ -2619,7 +2655,11 @@
       <c r="E2" s="1" t="inlineStr"/>
       <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" s="1" t="inlineStr"/>
-      <c r="H2" s="1" t="inlineStr"/>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
@@ -2778,7 +2818,11 @@
       <c r="E3" s="1" t="inlineStr"/>
       <c r="F3" s="1" t="inlineStr"/>
       <c r="G3" s="1" t="inlineStr"/>
-      <c r="H3" s="1" t="inlineStr"/>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
@@ -2937,7 +2981,11 @@
       <c r="E4" s="1" t="inlineStr"/>
       <c r="F4" s="1" t="inlineStr"/>
       <c r="G4" s="1" t="inlineStr"/>
-      <c r="H4" s="1" t="inlineStr"/>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>
@@ -3432,7 +3480,11 @@
       <c r="E2" s="1" t="inlineStr"/>
       <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" s="1" t="inlineStr"/>
-      <c r="H2" s="1" t="inlineStr"/>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>79685590315</t>
+        </is>
+      </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
           <t>Москва, Ижорская ул., 15с2</t>

--- a/avito-feed-construction/fleet-construction.xlsx
+++ b/avito-feed-construction/fleet-construction.xlsx
@@ -428,8 +428,8 @@
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
     <col width="40" customWidth="1" min="13" max="13"/>
     <col width="25" customWidth="1" min="14" max="14"/>
@@ -793,8 +793,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr"/>
-      <c r="K2" s="1" t="inlineStr"/>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -961,8 +969,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr"/>
-      <c r="K3" s="1" t="inlineStr"/>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -1129,8 +1145,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr"/>
-      <c r="K4" s="1" t="inlineStr"/>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -1297,8 +1321,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr"/>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -1465,8 +1497,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr"/>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -1633,8 +1673,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr"/>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="L7" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -1801,8 +1849,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="J8" s="1" t="inlineStr"/>
-      <c r="K8" s="1" t="inlineStr"/>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -1969,8 +2025,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="J9" s="1" t="inlineStr"/>
-      <c r="K9" s="1" t="inlineStr"/>
+      <c r="J9" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="K9" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="L9" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -2137,8 +2201,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr"/>
-      <c r="K10" s="1" t="inlineStr"/>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="K10" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="L10" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -2306,8 +2378,8 @@
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
     <col width="40" customWidth="1" min="13" max="13"/>
     <col width="25" customWidth="1" min="14" max="14"/>
@@ -2665,8 +2737,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr"/>
-      <c r="K2" s="1" t="inlineStr"/>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -2828,8 +2908,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr"/>
-      <c r="K3" s="1" t="inlineStr"/>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="L3" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -2991,8 +3079,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr"/>
-      <c r="K4" s="1" t="inlineStr"/>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>
@@ -3155,8 +3251,8 @@
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
     <col width="40" customWidth="1" min="13" max="13"/>
     <col width="25" customWidth="1" min="14" max="14"/>
@@ -3490,8 +3586,16 @@
           <t>Москва, Ижорская ул., 15с2</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr"/>
-      <c r="K2" s="1" t="inlineStr"/>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>55.8958019</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>37.5237956</t>
+        </is>
+      </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
           <t>По телефону и в сообщениях</t>

--- a/avito-feed-construction/fleet-construction.xlsx
+++ b/avito-feed-construction/fleet-construction.xlsx
@@ -778,7 +778,11 @@
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="D2" s="1" t="inlineStr"/>
       <c r="E2" s="1" t="inlineStr"/>
       <c r="F2" s="1" t="inlineStr"/>
@@ -954,7 +958,11 @@
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr"/>
-      <c r="C3" s="1" t="inlineStr"/>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="D3" s="1" t="inlineStr"/>
       <c r="E3" s="1" t="inlineStr"/>
       <c r="F3" s="1" t="inlineStr"/>
@@ -1130,7 +1138,11 @@
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr"/>
-      <c r="C4" s="1" t="inlineStr"/>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="D4" s="1" t="inlineStr"/>
       <c r="E4" s="1" t="inlineStr"/>
       <c r="F4" s="1" t="inlineStr"/>
@@ -1306,7 +1318,11 @@
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr"/>
-      <c r="C5" s="1" t="inlineStr"/>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="D5" s="1" t="inlineStr"/>
       <c r="E5" s="1" t="inlineStr"/>
       <c r="F5" s="1" t="inlineStr"/>
@@ -1482,7 +1498,11 @@
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr"/>
-      <c r="C6" s="1" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="D6" s="1" t="inlineStr"/>
       <c r="E6" s="1" t="inlineStr"/>
       <c r="F6" s="1" t="inlineStr"/>
@@ -1658,7 +1678,11 @@
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="D7" s="1" t="inlineStr"/>
       <c r="E7" s="1" t="inlineStr"/>
       <c r="F7" s="1" t="inlineStr"/>
@@ -1834,7 +1858,11 @@
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr"/>
-      <c r="C8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="D8" s="1" t="inlineStr"/>
       <c r="E8" s="1" t="inlineStr"/>
       <c r="F8" s="1" t="inlineStr"/>
@@ -2010,7 +2038,11 @@
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr"/>
-      <c r="C9" s="1" t="inlineStr"/>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="D9" s="1" t="inlineStr"/>
       <c r="E9" s="1" t="inlineStr"/>
       <c r="F9" s="1" t="inlineStr"/>
@@ -2186,7 +2218,11 @@
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr"/>
-      <c r="C10" s="1" t="inlineStr"/>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="D10" s="1" t="inlineStr"/>
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr"/>
@@ -2722,7 +2758,11 @@
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="D2" s="1" t="inlineStr"/>
       <c r="E2" s="1" t="inlineStr"/>
       <c r="F2" s="1" t="inlineStr"/>
@@ -2893,7 +2933,11 @@
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr"/>
-      <c r="C3" s="1" t="inlineStr"/>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="D3" s="1" t="inlineStr"/>
       <c r="E3" s="1" t="inlineStr"/>
       <c r="F3" s="1" t="inlineStr"/>
@@ -3064,7 +3108,11 @@
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr"/>
-      <c r="C4" s="1" t="inlineStr"/>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="D4" s="1" t="inlineStr"/>
       <c r="E4" s="1" t="inlineStr"/>
       <c r="F4" s="1" t="inlineStr"/>
@@ -3571,7 +3619,11 @@
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="D2" s="1" t="inlineStr"/>
       <c r="E2" s="1" t="inlineStr"/>
       <c r="F2" s="1" t="inlineStr"/>
